--- a/GLAPIBasic/Docker/BaseDB.xlsx
+++ b/GLAPIBasic/Docker/BaseDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GLAPIBasic\GLAPIBasic\Docker\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79C2E216-2FD5-4BBA-A401-D029152C31D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4DB9EE-8015-48E7-B761-2D538ECC346D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
   <si>
     <t>用户ID</t>
     <phoneticPr fontId="2"/>
@@ -385,6 +385,14 @@
   </si>
   <si>
     <t>bytea</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>用户角色表</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>角色显示名</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -805,15 +813,6 @@
       <c r="B2" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
@@ -832,7 +831,13 @@
         <v>11</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="K3" s="1" t="s">
         <v>6</v>
@@ -848,6 +853,9 @@
       <c r="B4" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="G4" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="K4" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,6 +873,9 @@
       <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="G5" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="O5" s="4" t="s">
         <v>29</v>
       </c>
@@ -959,6 +970,21 @@
     <row r="18" spans="1:7">
       <c r="A18" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7">
